--- a/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T14:27:25+00:00</t>
+    <t>2024-11-11T10:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1368,28 +1368,28 @@
     <t>Bundle.entry:Hauptversicherter.response.outcome</t>
   </si>
   <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation</t>
-  </si>
-  <si>
-    <t>ÜberweisendeOrganisation</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.link</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.fullUrl</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.resource</t>
+    <t>Bundle.entry:UeberweisendeOrganisation</t>
+  </si>
+  <si>
+    <t>UeberweisendeOrganisation</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.resource</t>
   </si>
   <si>
     <t xml:space="preserve">Organization {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization}
@@ -1411,79 +1411,79 @@
     <t>Entity, Role, or Act,Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.mode</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.search.score</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.method</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.url</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.ifMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.status</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.location</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.etag</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.lastModified</t>
-  </si>
-  <si>
-    <t>Bundle.entry:ÜberweisendeOrganisation.response.outcome</t>
+    <t>Bundle.entry:UeberweisendeOrganisation.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:UeberweisendeOrganisation.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -1827,9 +1827,9 @@
   <dimension ref="A1:AN210"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="64.4296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="65.55859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.0078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="26.98046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="28.78515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
